--- a/Hoàng/2025/T6/CÔNG TY TNHH TRIUMPH INTERNATIONAL VIỆT NAM (112-2025)/BV THIEN NHAN BG KSK - Công ty TNHH Triumph International Viêt Nam (1).xlsx
+++ b/Hoàng/2025/T6/CÔNG TY TNHH TRIUMPH INTERNATIONAL VIỆT NAM (112-2025)/BV THIEN NHAN BG KSK - Công ty TNHH Triumph International Viêt Nam (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T6\CÔNG TY TNHH TRIUMPH INTERNATIONAL VIỆT NAM (112-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F21A7A8-4B4F-449C-8EB6-B69A8984376F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE52ED2-35D9-49DB-9BA6-1F5F9833E426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -699,7 +699,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -850,6 +850,90 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -892,88 +976,10 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1358,48 +1364,48 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="70" t="s">
+      <c r="D1" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="72"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="59"/>
     </row>
     <row r="2" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="72"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="59"/>
     </row>
     <row r="3" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="72"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="59"/>
     </row>
     <row r="4" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="72"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="59"/>
     </row>
     <row r="5" spans="1:12" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="75"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="62"/>
     </row>
     <row r="6" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="5"/>
@@ -1410,15 +1416,15 @@
       <c r="G6" s="8"/>
     </row>
     <row r="7" spans="1:12" s="4" customFormat="1" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="76" t="s">
+      <c r="A7" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="76"/>
-      <c r="C7" s="76"/>
-      <c r="D7" s="76"/>
-      <c r="E7" s="76"/>
-      <c r="F7" s="76"/>
-      <c r="G7" s="76"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -1441,29 +1447,29 @@
     </row>
     <row r="9" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13"/>
-      <c r="B9" s="77" t="s">
+      <c r="B9" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="J9" s="14"/>
       <c r="K9" s="14"/>
     </row>
     <row r="10" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="79"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="80"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="67"/>
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
       <c r="J10" s="15"/>
@@ -1471,13 +1477,13 @@
       <c r="L10" s="15"/>
     </row>
     <row r="11" spans="1:12" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="81"/>
-      <c r="B11" s="82"/>
-      <c r="C11" s="82"/>
-      <c r="D11" s="82"/>
-      <c r="E11" s="82"/>
-      <c r="F11" s="82"/>
-      <c r="G11" s="83"/>
+      <c r="A11" s="68"/>
+      <c r="B11" s="69"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="70"/>
       <c r="H11" s="16"/>
       <c r="I11" s="16"/>
       <c r="J11" s="16"/>
@@ -1485,21 +1491,21 @@
       <c r="L11" s="16"/>
     </row>
     <row r="12" spans="1:12" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="57" t="s">
+      <c r="A12" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="59" t="s">
+      <c r="B12" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="60"/>
-      <c r="D12" s="57" t="s">
+      <c r="C12" s="88"/>
+      <c r="D12" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="92" t="s">
+      <c r="E12" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="92"/>
-      <c r="G12" s="93" t="s">
+      <c r="F12" s="79"/>
+      <c r="G12" s="80" t="s">
         <v>0</v>
       </c>
       <c r="H12" s="47"/>
@@ -1509,87 +1515,87 @@
       <c r="L12" s="16"/>
     </row>
     <row r="13" spans="1:12" s="18" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="58"/>
-      <c r="B13" s="61"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="58"/>
+      <c r="A13" s="86"/>
+      <c r="B13" s="89"/>
+      <c r="C13" s="90"/>
+      <c r="D13" s="86"/>
       <c r="E13" s="45" t="s">
         <v>62</v>
       </c>
       <c r="F13" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="94"/>
+      <c r="G13" s="81"/>
       <c r="H13" s="53"/>
     </row>
     <row r="14" spans="1:12" ht="39" x14ac:dyDescent="0.3">
-      <c r="A14" s="84">
+      <c r="A14" s="71">
         <v>1</v>
       </c>
-      <c r="B14" s="86" t="s">
+      <c r="B14" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="88" t="s">
+      <c r="C14" s="75" t="s">
         <v>48</v>
       </c>
       <c r="D14" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="E14" s="90">
+      <c r="E14" s="77">
         <v>100000</v>
       </c>
-      <c r="F14" s="90">
+      <c r="F14" s="77">
         <v>100000</v>
       </c>
-      <c r="G14" s="68"/>
+      <c r="G14" s="55"/>
       <c r="H14" s="19"/>
     </row>
     <row r="15" spans="1:12" ht="39" x14ac:dyDescent="0.3">
-      <c r="A15" s="85"/>
-      <c r="B15" s="87"/>
-      <c r="C15" s="89"/>
+      <c r="A15" s="72"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="76"/>
       <c r="D15" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="91"/>
-      <c r="F15" s="91"/>
-      <c r="G15" s="69"/>
+      <c r="E15" s="78"/>
+      <c r="F15" s="78"/>
+      <c r="G15" s="56"/>
       <c r="H15" s="19"/>
     </row>
     <row r="16" spans="1:12" ht="39" x14ac:dyDescent="0.3">
-      <c r="A16" s="85"/>
-      <c r="B16" s="87"/>
-      <c r="C16" s="89"/>
+      <c r="A16" s="72"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="76"/>
       <c r="D16" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="91"/>
-      <c r="F16" s="91"/>
-      <c r="G16" s="69"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="78"/>
+      <c r="G16" s="56"/>
       <c r="H16" s="19"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="85"/>
-      <c r="B17" s="87"/>
-      <c r="C17" s="89"/>
+      <c r="A17" s="72"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="76"/>
       <c r="D17" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="91"/>
-      <c r="F17" s="91"/>
-      <c r="G17" s="69"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="56"/>
       <c r="H17" s="20"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="85"/>
-      <c r="B18" s="87"/>
-      <c r="C18" s="89"/>
+      <c r="A18" s="72"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="76"/>
       <c r="D18" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="91"/>
-      <c r="F18" s="91"/>
-      <c r="G18" s="69"/>
+      <c r="E18" s="78"/>
+      <c r="F18" s="78"/>
+      <c r="G18" s="56"/>
       <c r="H18" s="20"/>
     </row>
     <row r="19" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1715,10 +1721,10 @@
       <c r="D24" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="44">
+      <c r="E24" s="96">
         <v>50000</v>
       </c>
-      <c r="F24" s="44">
+      <c r="F24" s="96">
         <v>50000</v>
       </c>
       <c r="G24" s="23"/>
@@ -1735,8 +1741,8 @@
       <c r="D25" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="95"/>
-      <c r="F25" s="95"/>
+      <c r="E25" s="97"/>
+      <c r="F25" s="97"/>
       <c r="G25" s="23"/>
       <c r="H25" s="20"/>
     </row>
@@ -1756,7 +1762,7 @@
       <c r="E26" s="44">
         <v>41000</v>
       </c>
-      <c r="F26" s="95"/>
+      <c r="F26" s="54"/>
       <c r="G26" s="23"/>
       <c r="H26" s="20"/>
     </row>
@@ -1793,7 +1799,7 @@
       <c r="D28" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="95"/>
+      <c r="E28" s="54"/>
       <c r="F28" s="44" t="s">
         <v>51</v>
       </c>
@@ -1811,7 +1817,7 @@
       <c r="D29" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="E29" s="95"/>
+      <c r="E29" s="54"/>
       <c r="F29" s="44" t="s">
         <v>51</v>
       </c>
@@ -1849,7 +1855,7 @@
       <c r="D31" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="E31" s="95"/>
+      <c r="E31" s="54"/>
       <c r="F31" s="44">
         <v>183000</v>
       </c>
@@ -1889,7 +1895,7 @@
       <c r="D33" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="E33" s="95"/>
+      <c r="E33" s="54"/>
       <c r="F33" s="44">
         <v>130000</v>
       </c>
@@ -1932,7 +1938,7 @@
       <c r="E35" s="44">
         <v>272000</v>
       </c>
-      <c r="F35" s="95"/>
+      <c r="F35" s="54"/>
       <c r="G35" s="23"/>
       <c r="H35" s="20"/>
     </row>
@@ -1957,12 +1963,12 @@
       <c r="H36" s="20"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="54" t="s">
+      <c r="A37" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="55"/>
-      <c r="C37" s="55"/>
-      <c r="D37" s="56"/>
+      <c r="B37" s="83"/>
+      <c r="C37" s="83"/>
+      <c r="D37" s="84"/>
       <c r="E37" s="24">
         <f>SUM(E14:E36)</f>
         <v>1000000</v>
@@ -1986,66 +1992,66 @@
     </row>
     <row r="39" spans="1:8" s="26" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="27"/>
-      <c r="B39" s="66" t="s">
+      <c r="B39" s="94" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="66"/>
-      <c r="D39" s="66"/>
-      <c r="E39" s="66"/>
-      <c r="F39" s="66"/>
-      <c r="G39" s="66"/>
+      <c r="C39" s="94"/>
+      <c r="D39" s="94"/>
+      <c r="E39" s="94"/>
+      <c r="F39" s="94"/>
+      <c r="G39" s="94"/>
     </row>
     <row r="40" spans="1:8" s="8" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="66" t="s">
+      <c r="B40" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="66"/>
+      <c r="C40" s="94"/>
+      <c r="D40" s="94"/>
+      <c r="E40" s="94"/>
+      <c r="F40" s="94"/>
+      <c r="G40" s="94"/>
     </row>
     <row r="41" spans="1:8" s="29" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="28"/>
-      <c r="B41" s="67" t="s">
+      <c r="B41" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="C41" s="67"/>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
+      <c r="C41" s="95"/>
+      <c r="D41" s="95"/>
+      <c r="E41" s="95"/>
+      <c r="F41" s="95"/>
+      <c r="G41" s="95"/>
     </row>
     <row r="42" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="26"/>
-      <c r="B42" s="66" t="s">
+      <c r="B42" s="94" t="s">
         <v>29</v>
       </c>
-      <c r="C42" s="66"/>
-      <c r="D42" s="66"/>
-      <c r="E42" s="66"/>
-      <c r="F42" s="66"/>
-      <c r="G42" s="66"/>
+      <c r="C42" s="94"/>
+      <c r="D42" s="94"/>
+      <c r="E42" s="94"/>
+      <c r="F42" s="94"/>
+      <c r="G42" s="94"/>
     </row>
     <row r="43" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26"/>
-      <c r="B43" s="63" t="s">
+      <c r="B43" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="C43" s="65"/>
-      <c r="D43" s="64"/>
+      <c r="C43" s="93"/>
+      <c r="D43" s="92"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="8"/>
     </row>
     <row r="44" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="26"/>
-      <c r="B44" s="63" t="s">
+      <c r="B44" s="91" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="65"/>
-      <c r="D44" s="65"/>
-      <c r="E44" s="65"/>
+      <c r="C44" s="93"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
       <c r="F44" s="46"/>
       <c r="G44" s="8"/>
     </row>
@@ -2062,10 +2068,10 @@
     </row>
     <row r="46" spans="1:8" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="26"/>
-      <c r="B46" s="63" t="s">
+      <c r="B46" s="91" t="s">
         <v>33</v>
       </c>
-      <c r="C46" s="64"/>
+      <c r="C46" s="92"/>
       <c r="D46" s="30"/>
       <c r="E46" s="37"/>
       <c r="F46" s="37"/>
@@ -2073,10 +2079,10 @@
     </row>
     <row r="47" spans="1:8" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="26"/>
-      <c r="B47" s="63" t="s">
+      <c r="B47" s="91" t="s">
         <v>52</v>
       </c>
-      <c r="C47" s="64"/>
+      <c r="C47" s="92"/>
       <c r="D47" s="30"/>
       <c r="E47" s="37"/>
       <c r="F47" s="37"/>
@@ -2084,29 +2090,17 @@
     </row>
     <row r="48" spans="1:8" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="26"/>
-      <c r="B48" s="63" t="s">
+      <c r="B48" s="91" t="s">
         <v>34</v>
       </c>
-      <c r="C48" s="64"/>
+      <c r="C48" s="92"/>
       <c r="D48" s="30"/>
       <c r="E48" s="37"/>
       <c r="F48" s="37"/>
       <c r="G48" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="G14:G18"/>
-    <mergeCell ref="D1:G5"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="A10:G11"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="C14:C18"/>
-    <mergeCell ref="E14:E18"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="F14:F18"/>
-    <mergeCell ref="G12:G13"/>
+  <mergeCells count="27">
     <mergeCell ref="A37:D37"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="B12:C13"/>
@@ -2120,6 +2114,20 @@
     <mergeCell ref="B41:G41"/>
     <mergeCell ref="B42:G42"/>
     <mergeCell ref="B43:D43"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G14:G18"/>
+    <mergeCell ref="D1:G5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="A10:G11"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="C14:C18"/>
+    <mergeCell ref="E14:E18"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="F14:F18"/>
+    <mergeCell ref="G12:G13"/>
   </mergeCells>
   <pageMargins left="0.28000000000000003" right="0.12" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="47" orientation="portrait" r:id="rId1"/>
